--- a/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2023_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2023_o_higgins.xlsx
@@ -146,7 +146,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:32</t>
+    <t xml:space="preserve">2026-09-10 01:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2023_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2023_o_higgins.xlsx
@@ -146,7 +146,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:49</t>
+    <t xml:space="preserve">2026-09-12 23:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2023_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2023_o_higgins.xlsx
@@ -146,7 +146,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 23:00</t>
+    <t xml:space="preserve">2026-09-23 15:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2023_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2023_o_higgins.xlsx
@@ -134,7 +134,7 @@
     <t xml:space="preserve">Peralillo</t>
   </si>
   <si>
-    <t xml:space="preserve">Marchihue</t>
+    <t xml:space="preserve">Marchigüe</t>
   </si>
   <si>
     <t xml:space="preserve">Campo</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:52</t>
+    <t xml:space="preserve">2026-10-04 10:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2023_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2023_o_higgins.xlsx
@@ -146,7 +146,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:52</t>
+    <t xml:space="preserve">2026-10-05 17:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
